--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ago-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ago-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ago-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.911.731-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3057,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3122,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3187,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3313,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3443,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3508,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3634,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3947,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4012,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4272,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4337,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4402,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4532,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4597,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4662,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4727,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4979,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5044,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5170,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5357,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5487,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5678,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5865,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5930,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5995,11 @@
           <t>77.911.731-6</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6125,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6316,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6381,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6446,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6511,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6576,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6702,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6767,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6893,11 @@
           <t>77.883.662-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6958,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7084,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7336,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7401,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7466,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7592,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7657,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7974,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8039,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8104,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8295,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8360,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8425,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8490,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8555,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8681,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8811,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8876,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8941,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9132,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9197,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9262,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9327,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9522,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9652,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9717,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9782,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10286,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10351,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10416,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10542,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10668,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10733,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10798,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10863,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10993,11 @@
           <t>77.883.662-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11058,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11245,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11310,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11375,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11505,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11570,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11635,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11887,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11952,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12407,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12472,11 @@
           <t>77.911.731-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12537,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12663,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12728,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12793,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12858,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12988,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13244,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13309,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13496,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13744,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13809,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13874,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13939,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14004,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14069,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14256,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14447,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14512,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14638,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14703,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14768,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14894,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14959,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15024,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15089,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15154,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15280,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15406,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15471,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15536,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15601,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15666,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15731,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15857,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16113,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16178,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16243,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16308,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16499,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16564,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16694,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16759,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16824,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16954,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17084,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17149,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17344,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17470,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17726,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17856,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17921,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18112,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18177,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18368,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18433,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18559,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18811,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18876,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18941,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19006,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19071,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19136,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19262,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19327,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19514,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19640,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19766,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19831,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19896,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20205,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20270,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20335,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20400,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20465,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20778,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20904,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20969,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21034,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21160,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21347,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21412,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21538,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21603,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21668,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21794,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21859,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22050,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22115,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22363,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22428,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22493,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22680,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22745,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22871,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23180,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23245,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23310,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23436,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23501,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23566,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23631,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23696,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23761,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23826,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23891,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24208,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24273,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24590,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24655,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24907,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25037,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25232,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25297,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25427,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25492,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25622,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25687,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25752,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26008,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26199,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26264,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26329,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26516,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26581,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26646,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26833,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26959,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27150,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27215,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27540,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27731,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27861,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27926,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28056,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28121,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28186,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28251,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28316,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28381,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28507,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28572,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28637,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28702,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28767,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28897,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29084,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29149,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29214,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29340,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29466,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29531,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29596,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29661,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29726,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29791,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29982,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30112,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30555,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30620,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30685,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30750,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30880,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30945,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31010,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31075,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31262,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31327,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31453,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31583,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31709,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31774,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31839,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31969,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32164,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32229,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32294,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32359,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32424,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32489,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32615,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32741,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32806,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32871,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32997,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33123,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33188,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33253,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33318,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33383,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33448,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33639,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33704,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33769,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33834,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33899,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34025,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34090,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34155,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34285,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34411,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34541,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34732,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34797,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34862,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34927,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35057,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35122,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35313,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35443,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35569,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35634,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35825,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35951,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36199,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36451,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36516,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36581,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36898,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36963,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +37028,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +37093,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37158,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37288,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37414,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37479,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37544,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37609,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37796,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37861,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37926,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37991,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38056,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38121,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +38186,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38316,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
